--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486318_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486318_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0757</v>
+        <v>1.779</v>
       </c>
       <c r="E2" t="n">
-        <v>3.387</v>
+        <v>3.2753</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3113</v>
+        <v>-1.4962</v>
       </c>
       <c r="G2" t="n">
         <v>0.1138</v>
@@ -610,13 +610,13 @@
         <v>0.6525</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7227</v>
+        <v>0.426</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4146</v>
+        <v>0.3028</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3081</v>
+        <v>0.1232</v>
       </c>
       <c r="V2" t="n">
         <v>1.6743</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.684</v>
+        <v>1.2476</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7363</v>
+        <v>2.0225</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0523</v>
+        <v>-0.7749</v>
       </c>
       <c r="G3" t="n">
         <v>-1.181</v>
@@ -688,13 +688,13 @@
         <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4746</v>
+        <v>0.0382</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2882</v>
+        <v>0.5744</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8137</v>
+        <v>-0.5363</v>
       </c>
       <c r="V3" t="n">
         <v>1.5204</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.7622</v>
+        <v>-0.2158</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1881</v>
+        <v>2.7037</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.9503</v>
+        <v>-2.9195</v>
       </c>
       <c r="G4" t="n">
         <v>-1.7055</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4265</v>
+        <v>0.1199</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1334</v>
+        <v>0.3822</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2931</v>
+        <v>-0.2623</v>
       </c>
       <c r="V4" t="n">
         <v>0.9347</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.3096</v>
+        <v>-1.4406</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4008</v>
+        <v>0.1772</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7104</v>
+        <v>-1.6179</v>
       </c>
       <c r="G5" t="n">
         <v>-1.325</v>
@@ -844,13 +844,13 @@
         <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2244</v>
+        <v>-0.3554</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0769</v>
+        <v>-0.3004</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1475</v>
+        <v>-0.055</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1952</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3466</v>
+        <v>-2.2724</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5099</v>
+        <v>0.4608</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.8565</v>
+        <v>-2.7332</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6449</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8633</v>
+        <v>-0.0625</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1392</v>
+        <v>0.0901</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2759</v>
+        <v>-0.1526</v>
       </c>
       <c r="V6" t="n">
         <v>-1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.7989</v>
+        <v>-4.11</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5068</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.2921</v>
+        <v>-3.2305</v>
       </c>
       <c r="G7" t="n">
         <v>-4.1326</v>
@@ -1000,13 +1000,13 @@
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4694</v>
+        <v>-0.7805</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3014</v>
+        <v>-0.6741</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.168</v>
+        <v>-0.1064</v>
       </c>
       <c r="V7" t="n">
         <v>0.5857</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.0426</v>
+        <v>-6.344</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.7008</v>
+        <v>-4.6323</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3419</v>
+        <v>-1.7117</v>
       </c>
       <c r="G8" t="n">
         <v>-2.7099</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7124</v>
+        <v>0.411</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1406</v>
+        <v>0.2091</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5718</v>
+        <v>0.2019</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5649999999999999</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.8667</v>
+        <v>-6.6162</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3515</v>
+        <v>-2.7927</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.5152</v>
+        <v>-3.8234</v>
       </c>
       <c r="G9" t="n">
         <v>-2.693</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7811</v>
+        <v>-0.5306</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0959</v>
+        <v>-0.5371</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3148</v>
+        <v>0.0066</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5649999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.5036</v>
+        <v>-8.5557</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.7294</v>
+        <v>-7.0589</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7742</v>
+        <v>-1.4968</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2688</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3616</v>
+        <v>-0.4137</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.399</v>
+        <v>0.2716</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9627</v>
+        <v>-0.6853</v>
       </c>
       <c r="V10" t="n">
         <v>1.8695</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-26.8705</v>
+        <v>-26.5281</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.066400000000002</v>
+        <v>-6.7239</v>
       </c>
       <c r="F11" t="n">
-        <v>-19.8042</v>
+        <v>-19.8041</v>
       </c>
       <c r="G11" t="n">
         <v>-17.5469</v>
@@ -1312,10 +1312,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.49</v>
+        <v>-1.1476</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0239999999999998</v>
+        <v>0.3185999999999998</v>
       </c>
       <c r="U11" t="n">
         <v>-1.4662</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.5814</v>
+        <v>9.897399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>9.793799999999999</v>
+        <v>10.0173</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2123</v>
+        <v>-0.1199</v>
       </c>
       <c r="G12" t="n">
         <v>8.192500000000001</v>
@@ -1390,13 +1390,13 @@
         <v>1.9576</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3734</v>
+        <v>-0.0574</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.399</v>
+        <v>-0.1754</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0256</v>
+        <v>0.1181</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1952</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1851</v>
+        <v>5.7792</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9023</v>
+        <v>3.6421</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2828</v>
+        <v>2.1371</v>
       </c>
       <c r="G13" t="n">
-        <v>3.066</v>
+        <v>4.1688</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7854</v>
+        <v>2.2324</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2805</v>
+        <v>1.9364</v>
       </c>
       <c r="J13" t="n">
-        <v>3.0422</v>
+        <v>3.847</v>
       </c>
       <c r="K13" t="n">
         <v>1.7218</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3204</v>
+        <v>2.1253</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0238</v>
+        <v>0.3218</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0636</v>
+        <v>0.5107</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0399</v>
+        <v>-0.1889</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6101</v>
+        <v>1.9576</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.6101</v>
+        <v>1.9576</v>
       </c>
       <c r="S13" t="n">
-        <v>1.769</v>
+        <v>-0.152</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5997</v>
+        <v>-0.4002</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1693</v>
+        <v>0.2481</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.2599</v>
+        <v>-0.1952</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5204</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8864</v>
+        <v>3.8815</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0833</v>
+        <v>2.3435</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8031</v>
+        <v>1.5379</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1688</v>
+        <v>3.066</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2324</v>
+        <v>1.7854</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9364</v>
+        <v>1.2805</v>
       </c>
       <c r="J14" t="n">
-        <v>3.847</v>
+        <v>3.0422</v>
       </c>
       <c r="K14" t="n">
         <v>1.7218</v>
       </c>
       <c r="L14" t="n">
-        <v>2.1253</v>
+        <v>1.3204</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3218</v>
+        <v>0.0238</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5107</v>
+        <v>0.0636</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1889</v>
+        <v>-0.0399</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9576</v>
+        <v>2.6101</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9576</v>
+        <v>2.6101</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0448</v>
+        <v>0.4654</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9589</v>
+        <v>0.0409</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0858</v>
+        <v>0.4245</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1952</v>
+        <v>-2.2599</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3904</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2049</v>
+        <v>3.8734</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4311</v>
+        <v>3.3891</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.4843</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9117</v>
+        <v>2.367</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3101</v>
+        <v>-1.4842</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6016</v>
+        <v>3.8512</v>
       </c>
       <c r="J15" t="n">
-        <v>1.633</v>
+        <v>3.5353</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6935</v>
+        <v>-0.6538</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9395</v>
+        <v>4.1891</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-1.1683</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3834</v>
+        <v>-0.8304</v>
       </c>
       <c r="O15" t="n">
         <v>-0.3379</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1751</v>
+        <v>0.6525</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0119</v>
+        <v>-0.2761</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6682</v>
+        <v>-0.1887</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.68</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7694</v>
+        <v>3.7142</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5008</v>
+        <v>2.7606</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2686</v>
+        <v>0.9536</v>
       </c>
       <c r="G16" t="n">
-        <v>2.367</v>
+        <v>0.9117</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4842</v>
+        <v>0.3101</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8512</v>
+        <v>0.6016</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5353</v>
+        <v>1.633</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6538</v>
+        <v>0.6935</v>
       </c>
       <c r="L16" t="n">
-        <v>4.1891</v>
+        <v>0.9395</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1683</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8304</v>
+        <v>-0.3834</v>
       </c>
       <c r="O16" t="n">
         <v>-0.3379</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6525</v>
+        <v>2.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3801</v>
+        <v>-0.5026</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0769</v>
+        <v>-0.0024</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3032</v>
+        <v>-0.5002</v>
       </c>
       <c r="V16" t="n">
         <v>1.13</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7326</v>
+        <v>1.6748</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4639</v>
+        <v>0.1286</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2687</v>
+        <v>1.5462</v>
       </c>
       <c r="G17" t="n">
         <v>1.5611</v>
@@ -1780,13 +1780,13 @@
         <v>2.3926</v>
       </c>
       <c r="S17" t="n">
-        <v>0.519</v>
+        <v>0.4612</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7367</v>
+        <v>0.4014</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2176</v>
+        <v>0.0598</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5649999999999999</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. UGOCHUKWU</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9358</v>
+        <v>1.3394</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4658</v>
+        <v>0.5616</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.53</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4858</v>
+        <v>-1.2517</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2523</v>
+        <v>-0.7847</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2335</v>
+        <v>-0.467</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1127</v>
+        <v>-0.43</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1127</v>
+        <v>-0.4499</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0199</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5985</v>
+        <v>-0.8217</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.365</v>
+        <v>-0.3348</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2335</v>
+        <v>-0.4869</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2041</v>
+        <v>0.286</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3531</v>
+        <v>0.4266</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.149</v>
+        <v>-0.1406</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2963</v>
+        <v>0.1031</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3324</v>
+        <v>-0.3734</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6287</v>
+        <v>0.4765</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2517</v>
+        <v>-0.7335</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7847</v>
+        <v>1.1008</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.467</v>
+        <v>-1.8344</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.43</v>
+        <v>-0.6258</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4499</v>
+        <v>1.5512</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0199</v>
+        <v>-2.177</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8217</v>
+        <v>-0.1077</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3348</v>
+        <v>-0.4504</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4869</v>
+        <v>0.3426</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7571</v>
+        <v>0.444</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4675</v>
+        <v>0.2524</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2896</v>
+        <v>0.1917</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>S. UGOCHUKWU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4402</v>
+        <v>0.0417</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4852</v>
+        <v>0.5717</v>
       </c>
       <c r="F20" t="n">
-        <v>0.045</v>
+        <v>-0.53</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7335</v>
+        <v>-0.4858</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1008</v>
+        <v>-0.2523</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8344</v>
+        <v>-0.2335</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6258</v>
+        <v>0.1127</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5512</v>
+        <v>0.1127</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.177</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1077</v>
+        <v>-0.5985</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4504</v>
+        <v>-0.365</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3426</v>
+        <v>-0.2335</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0993</v>
+        <v>0.31</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1406</v>
+        <v>0.4591</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2399</v>
+        <v>-0.149</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8591</v>
+        <v>-0.0781</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8367</v>
+        <v>-0.3897</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0224</v>
+        <v>0.3115</v>
       </c>
       <c r="G21" t="n">
         <v>-0.094</v>
@@ -2092,13 +2092,13 @@
         <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5052</v>
+        <v>0.2758</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0036</v>
+        <v>0.4506</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5088</v>
+        <v>-0.1749</v>
       </c>
       <c r="V21" t="n">
         <v>-1.13</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.973</v>
+        <v>-1.2118</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.245</v>
+        <v>-3.0215</v>
       </c>
       <c r="F22" t="n">
-        <v>2.272</v>
+        <v>1.8097</v>
       </c>
       <c r="G22" t="n">
         <v>0.4514</v>
@@ -2170,13 +2170,13 @@
         <v>2.3926</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9247</v>
+        <v>0.6859</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0769</v>
+        <v>0.1466</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0016</v>
+        <v>0.5392</v>
       </c>
       <c r="V22" t="n">
         <v>-1.479</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4491</v>
+        <v>-1.399</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0625</v>
+        <v>0.1742</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5115</v>
+        <v>-1.5732</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6064000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2449</v>
+        <v>0.295</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0565</v>
+        <v>0.0553</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3014</v>
+        <v>0.2397</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>26.8705</v>
+        <v>27.6158</v>
       </c>
       <c r="E24" t="n">
-        <v>19.8042</v>
+        <v>19.8041</v>
       </c>
       <c r="F24" t="n">
-        <v>7.0664</v>
+        <v>7.811399999999999</v>
       </c>
       <c r="G24" t="n">
         <v>17.5471</v>
@@ -2302,7 +2302,7 @@
         <v>22.2818</v>
       </c>
       <c r="K24" t="n">
-        <v>5.4161</v>
+        <v>5.416100000000001</v>
       </c>
       <c r="L24" t="n">
         <v>16.8658</v>
@@ -2326,16 +2326,16 @@
         <v>20.6634</v>
       </c>
       <c r="S24" t="n">
-        <v>1.4899</v>
+        <v>2.2352</v>
       </c>
       <c r="T24" t="n">
         <v>1.4662</v>
       </c>
       <c r="U24" t="n">
-        <v>0.02400000000000013</v>
+        <v>0.769</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.1293</v>
+        <v>-4.129300000000001</v>
       </c>
       <c r="W24" t="n">
         <v>4.7566</v>
